--- a/GPIOBoard/bom/GPIOBoard.xlsx
+++ b/GPIOBoard/bom/GPIOBoard.xlsx
@@ -1,64 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\Robocon2025-PCB\GPIOBoard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\Robocon2025-PCB\GPIOBoard\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0FAB31-2D84-491B-93EF-9AEF87FBA99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A050F374-1FC9-443B-8EA4-C2E4C66B080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{5A796D7A-E576-48F8-9DE8-4C60006732EF}"/>
+    <workbookView xWindow="270" yWindow="1170" windowWidth="28530" windowHeight="7485" xr2:uid="{9555B947-0739-454E-89C8-3DBAE623C4C8}"/>
   </bookViews>
   <sheets>
     <sheet name="GPIOBoard" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
   <si>
     <t>Reference</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
     <t>Qty</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
     <t>4.7u</t>
   </si>
   <si>
+    <t>GRM188R60J226MEA0D</t>
+  </si>
+  <si>
     <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188R60J226MEA0D/4280542</t>
   </si>
   <si>
@@ -89,6 +79,12 @@
     <t>1u</t>
   </si>
   <si>
+    <t>GRM188D71H105ME01W</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188D71H105ME01W/22528412</t>
+  </si>
+  <si>
     <t>C9,C10</t>
   </si>
   <si>
@@ -173,15 +169,6 @@
     <t>https://www.digikey.jp/ja/products/detail/murata-electronics/BLM18KG601SN1D/1982766</t>
   </si>
   <si>
-    <t>H1,H2,H3,H4</t>
-  </si>
-  <si>
-    <t>MountingHole_Pad</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>J1,J2,J3,J4,J5,J6,J7,J8</t>
   </si>
   <si>
@@ -239,12 +226,6 @@
     <t>https://eleshop.jp/shop/g/g7AB411/</t>
   </si>
   <si>
-    <t>JP1</t>
-  </si>
-  <si>
-    <t>MCP2561/2FD selector</t>
-  </si>
-  <si>
     <t>R1,R2,R3,R4,R5,R6,R7,R8</t>
   </si>
   <si>
@@ -278,6 +259,9 @@
     <t>R19,R27</t>
   </si>
   <si>
+    <t>ESR03EZPJ431</t>
+  </si>
+  <si>
     <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ431/4051257?s=N4IgjCBcoCwGxVAYygMwIYBsDOBTANCAPZQDaIA7ABwAMATCALqEAOALlCAMpsBOAlgDsA5iAC%2BhMAE4qUxCBSQMOAsTIgaTCSDo0qAVnmLleQiUjkYAZhoACAPIALALbYmrDpBABVQfzb2qACyuOjYAK68uOKEALRy0ApQfOGq5uQQjNqxDImKKWnqhllxEHloWKZqFiBU8FpxMEYVKmbqVnUUCFnaueSAgwyAwwyA6wyArUaA6UZaQA</t>
   </si>
   <si>
@@ -302,7 +286,7 @@
     <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ121/1983454</t>
   </si>
   <si>
-    <t>R26</t>
+    <t>R26,R31</t>
   </si>
   <si>
     <t>10k</t>
@@ -323,9 +307,6 @@
     <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPF5900/20506305?s=N4IgjCBcpgbFoDGUBmBDANgZwKYBoQB7KAbRAGYBOAJgBZ4BdAgBwBcoQBlVgJwEsAdgHMQAXwJhKADkoIQySOmz4ipEAAYQDcSGrqpAVjkKluAsUhkDldQAIA8gAsAtli0t2kEAFUBfVvYoALI4aFgArjw4YgQAtBDQ8qiYZqqWIFL0WjqxtMbJyuZq5JkA7Iw5sokKvOEqFmQQ2nHU%2BZC19WpG2jqt6YCDDIDDDIDrDICtRoDpRtlAA</t>
   </si>
   <si>
-    <t>R31</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -429,133 +410,13 @@
   </si>
   <si>
     <t>https://www.digikey.jp/ja/products/detail/murata-electronics/XRCGB32M000F1SADR0/21662918?s=N4IgTCBcDaIBoCUDCBxAQgZjAWQAz4DEBGAZQEEARBXEAXQF8g</t>
-  </si>
-  <si>
-    <t>合計</t>
-    <rPh sb="0" eb="2">
-      <t>ゴウケイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Price*Qty</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>基板以外で必要なもの</t>
-    <rPh sb="0" eb="2">
-      <t>キバン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>CAN入力</t>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>FC-06P</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/g79J413/</t>
-  </si>
-  <si>
-    <t>FC-06/SR</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/g79J415/</t>
-  </si>
-  <si>
-    <t>SHR-04V-S-B</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/jst-sales-america-inc/SHR-04V-S-B/759868</t>
-  </si>
-  <si>
-    <t>SSH-003T-P0.2-H</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/jst-sales-america-inc/SSH-003T-P0-2-H/2804713</t>
-  </si>
-  <si>
-    <t>QI-4</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/g4AM144/</t>
-  </si>
-  <si>
-    <t>QI-ZU</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/g4AM14A/</t>
-  </si>
-  <si>
-    <t>シリコンワイヤーより線 L-2m AWG28 (黒)</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/gF47V1C/</t>
-  </si>
-  <si>
-    <t>ESR03EZPJ390</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ390/4051248</t>
-  </si>
-  <si>
-    <t>ESR03EZPF6650</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPF6650/21731250</t>
-  </si>
-  <si>
-    <t>SHコネクタ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/gE23139/</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/gE23133/</t>
-  </si>
-  <si>
-    <t>https://eleshop.jp/shop/g/gE2313A/</t>
-  </si>
-  <si>
-    <t>GRM188R60J226MEA0D</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>GRM188D71H105ME01W</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188D71H105ME01W/22528412</t>
-  </si>
-  <si>
-    <t>ESR03EZPJ431</t>
-    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
-    <numFmt numFmtId="177" formatCode="0.0_ "/>
-  </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,15 +576,6 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1022,7 +874,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1149,31 +1001,16 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1201,7 +1038,6 @@
     <cellStyle name="タイトル" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="チェック セル" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="どちらでもない" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="ハイパーリンク" xfId="42" builtinId="8"/>
     <cellStyle name="メモ" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="リンク セル" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
@@ -1547,16 +1383,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC0DBE7-D091-4525-A033-132485F534B2}">
-  <dimension ref="A1:G54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE49AAA5-75C8-4731-9D5A-90E564259C07}">
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
-    <col min="5" max="5" width="23.375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1575,1083 +1406,662 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>47</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>48</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>53</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12">
+        <v>16</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+      <c r="F13">
         <v>8</v>
       </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <f>F2*B2</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14">
+        <v>53</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15">
+        <v>110</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16">
+        <v>81</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17">
+        <v>62</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>22</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="1">
+        <v>300330</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19">
+        <v>22</v>
+      </c>
+      <c r="F19">
         <v>9</v>
       </c>
-      <c r="B3">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20">
+        <v>22</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="1">
+        <v>420430</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21">
+        <v>22</v>
+      </c>
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G37" si="0">F3*B3</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4">
-        <v>36</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23">
+        <v>22</v>
+      </c>
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5">
-        <v>47</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>22</v>
+      </c>
+      <c r="F24">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25">
+        <v>600</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25">
         <v>22</v>
       </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>48</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9">
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10">
-        <v>30</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26">
+        <v>22</v>
+      </c>
+      <c r="F26">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27">
+        <v>458</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28">
+        <v>87</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29">
+        <v>780</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30">
+        <v>63</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31">
+        <v>90</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32">
+        <v>202</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33">
+        <v>244</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34">
         <v>52</v>
       </c>
-      <c r="F14">
-        <v>65</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>520</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15">
+      <c r="F34">
         <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16">
-        <v>110</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17">
-        <v>81</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20">
-        <v>8</v>
-      </c>
-      <c r="C20">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20">
-        <v>22</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="0"/>
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21">
-        <v>9</v>
-      </c>
-      <c r="C21" s="1">
-        <v>300330</v>
-      </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21">
-        <v>22</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="0"/>
-        <v>198</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22">
-        <v>22</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>420430</v>
-      </c>
-      <c r="D23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E23" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23">
-        <v>22</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24">
-        <v>22</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>120</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25">
-        <v>22</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26">
-        <v>22</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>600</v>
-      </c>
-      <c r="D27" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27">
-        <v>22</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28">
-        <v>22</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29">
-        <v>22</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30">
-        <v>458</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="0"/>
-        <v>458</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" t="s">
-        <v>108</v>
-      </c>
-      <c r="F31">
-        <v>87</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>109</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" t="s">
-        <v>112</v>
-      </c>
-      <c r="F32">
-        <v>780</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33">
-        <v>63</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34">
-        <v>90</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" t="s">
-        <v>123</v>
-      </c>
-      <c r="F35">
-        <v>202</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="0"/>
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36">
-        <v>244</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="0"/>
-        <v>244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>128</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37">
-        <v>52</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="F39" t="s">
-        <v>132</v>
-      </c>
-      <c r="G39">
-        <f>SUM(G2:G37)</f>
-        <v>4712</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B41" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>136</v>
-      </c>
-      <c r="D42" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" t="s">
-        <v>138</v>
-      </c>
-      <c r="F42">
-        <v>92</v>
-      </c>
-      <c r="G42">
-        <f t="shared" ref="G42:G50" si="1">B42*F42</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>139</v>
-      </c>
-      <c r="E43" t="s">
-        <v>140</v>
-      </c>
-      <c r="F43">
-        <v>28</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="D44" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" t="s">
-        <v>142</v>
-      </c>
-      <c r="F44">
-        <v>16</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B45">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
-        <v>143</v>
-      </c>
-      <c r="E45" t="s">
-        <v>144</v>
-      </c>
-      <c r="F45">
-        <v>17</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="D46" t="s">
-        <v>145</v>
-      </c>
-      <c r="E46" t="s">
-        <v>146</v>
-      </c>
-      <c r="F46">
-        <v>24</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B47">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E47" t="s">
-        <v>148</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="1"/>
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>149</v>
-      </c>
-      <c r="E48" t="s">
-        <v>150</v>
-      </c>
-      <c r="F48">
-        <v>245</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="1"/>
-        <v>245</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B49">
-        <v>8</v>
-      </c>
-      <c r="D49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" t="s">
-        <v>152</v>
-      </c>
-      <c r="F49" s="3">
-        <v>22</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="1"/>
-        <v>176</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B50">
-        <v>8</v>
-      </c>
-      <c r="D50" t="s">
-        <v>153</v>
-      </c>
-      <c r="E50" t="s">
-        <v>154</v>
-      </c>
-      <c r="F50">
-        <v>23</v>
-      </c>
-      <c r="G50">
-        <f t="shared" si="1"/>
-        <v>184</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C52" t="s">
-        <v>155</v>
-      </c>
-      <c r="D52" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" t="s">
-        <v>156</v>
-      </c>
-      <c r="F52">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="D53" t="s">
-        <v>141</v>
-      </c>
-      <c r="E53" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="D54" t="s">
-        <v>143</v>
-      </c>
-      <c r="E54" t="s">
-        <v>158</v>
-      </c>
-      <c r="F54" s="4">
-        <f>125/10</f>
-        <v>12.5</v>
       </c>
     </row>
   </sheetData>
